--- a/sources/prototype_step9.xlsx
+++ b/sources/prototype_step9.xlsx
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">

--- a/sources/prototype_step9.xlsx
+++ b/sources/prototype_step9.xlsx
@@ -862,6 +862,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
@@ -939,6 +944,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
@@ -1006,6 +1016,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
@@ -1071,6 +1086,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>c4222188-365d-401c-a75a-8d64d256a8cc</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -8787,6 +8807,11 @@
       <c r="T99" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>4e36f2e9-e904-45da-b205-e22a2d153bbd</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">

--- a/sources/prototype_step9.xlsx
+++ b/sources/prototype_step9.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AD99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="114" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="114" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,62 +622,62 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Hell Press</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Hell Press</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Only throws on a hit in close range, damage will be 20 on out of throw range hit. Causes Guard Break on a block.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>86b861ce-3ac3-487f-80a6-10c207314ea1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>38bb5c58-f37a-4dba-827f-917a759aaf91</t>
         </is>
@@ -688,57 +694,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ground Zero</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Ground Zero</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>d9a31507-094f-45a3-93ed-8ead11b24715</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>704172e7-30a6-49bb-bbb3-a7027ba62c18</t>
         </is>
@@ -755,57 +761,57 @@
           <t>db+2+3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Body Smash</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Body Smash</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>118665d5-4093-4728-8b96-995728658c16</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1dfcb085-b045-4a3c-b19e-fb522eb428ee</t>
         </is>
@@ -822,62 +828,62 @@
           <t>2+4,db,d ,DF+2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Gigaton Punishment</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Ground Zero – Gigaton Punishment</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>30,49</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>The initial grab does no damage.</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>704172e7-30a6-49bb-bbb3-a7027ba62c18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -901,60 +907,65 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2+5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Tornado</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Tornado</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -978,55 +989,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Father's Love</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Father's Love</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>8,8,24</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>8,8,24</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1050,55 +1066,60 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Reverse Lift Slam</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Reverse Lift Slam</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>c4222188-365d-401c-a75a-8d64d256a8cc</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>c4222188-365d-401c-a75a-8d64d256a8cc</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1135,125 +1156,130 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="P12" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr">
+      <c r="Q12" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R12" s="1" t="inlineStr">
+      <c r="S12" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S12" s="1" t="inlineStr">
+      <c r="T12" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T12" s="1" t="inlineStr">
+      <c r="U12" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U12" s="1" t="inlineStr">
+      <c r="V12" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V12" s="1" t="inlineStr">
+      <c r="W12" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W12" s="1" t="inlineStr">
+      <c r="X12" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X12" s="1" t="inlineStr">
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB12" s="1" t="inlineStr">
+      <c r="AC12" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC12" s="1" t="inlineStr">
+      <c r="AD12" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1270,77 +1296,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>6d040c41-694f-42c9-a48d-e970baf8f39c</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>b903adac-7205-47ec-ab49-98736320d211</t>
         </is>
@@ -1357,77 +1383,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>df7ddc39-d982-404a-b1a6-5c20f25dc66e</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>3e61c500-63bd-453d-8f3e-fa44819c5fbf</t>
         </is>
@@ -1444,77 +1470,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>61c85e2f-9e6c-418a-8f93-3f3c81284363</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>817618f2-5cf5-473d-9940-9e48f6f1cf79</t>
         </is>
@@ -1531,77 +1557,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>8823dd50-a84e-4e05-ab2f-844d1e11ac60</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>ef07e047-89df-4f38-838b-ba8ea7807522</t>
         </is>
@@ -1618,77 +1644,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>cf54e060-70c7-4167-a1c6-5b6bb0aad3fa</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>58daaeea-cb50-428f-ad65-6e56101baf4f</t>
         </is>
@@ -1705,77 +1731,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>3844470c-aec8-45b5-b2c2-a57f7c42ef24</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>694566fe-f3fc-4f8f-8c4f-21ab7fdce8e9</t>
         </is>
@@ -1792,77 +1818,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>30fa6b95-a57e-4e90-a79d-11baa41931de</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>6d1347ac-bc30-4f99-9d00-c988367ebfc6</t>
         </is>
@@ -1879,77 +1905,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>bb677190-64cf-4f87-8e4b-998ad7e8620b</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>f290b88c-02b9-4a6c-9539-532cb69861a7</t>
         </is>
@@ -1966,77 +1992,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>5e9531b0-7140-41f7-88e5-dcaca646d696</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>af8b9ef7-6509-4d7f-b19e-a50c9ce2b613</t>
         </is>
@@ -2053,77 +2079,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>7a69dc23-dde2-4c09-9143-bd27a2f331c9</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>980d835b-8f38-47ed-84de-13a74abdaf3e</t>
         </is>
@@ -2140,77 +2166,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>bbbc3139-5b4c-4380-aa5a-7d12a1a6a983</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>4272d5bd-b7b0-4024-9fbf-6a388d6b967f</t>
         </is>
@@ -2227,77 +2253,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>dd6d184c-6832-4940-9f22-8739446041bd</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>a2b7f740-74b9-4cfb-8992-93e81d6e31e9</t>
         </is>
@@ -2314,77 +2340,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>869c9b11-dde2-4364-a0e1-d5e26aa93559</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>080bc451-67f4-492f-b14c-6d83ba472a79</t>
         </is>
@@ -2401,77 +2427,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>63d4635e-4706-47a1-9046-b57e24a76bd2</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>57752409-5188-4bd4-9ae0-a9469ffdb103</t>
         </is>
@@ -2488,77 +2514,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>c774e410-f9f0-4b07-bb3f-e1b8d90fb73b</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>71d5a832-9e95-40fd-bd9b-c6b13f990873</t>
         </is>
@@ -2575,77 +2601,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>5cf47f15-aa66-4d7d-b8e3-d89293be9e3d</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>ce6fcc03-5a1b-4386-adfa-91f08f73d035</t>
         </is>
@@ -2662,77 +2688,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>06e4eea9-5c05-4645-911a-75461aa574f1</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>c1e2ce94-f0b9-4b39-a203-77ff4137f43b</t>
         </is>
@@ -2749,77 +2775,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>3dad9b5f-02f4-4cae-9dcd-36defa662e7e</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>ea0e0833-0714-455b-8766-8c63d45029aa</t>
         </is>
@@ -2836,77 +2862,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>ddd8beb0-d5ca-4140-8c2d-6ccecff1150e</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>7dde22e7-b0d5-4499-b04a-13dd0ed0ca0e</t>
         </is>
@@ -2923,77 +2949,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>e8dd2793-1ab6-48e8-b669-4a5ef41c3649</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>c0dd3760-9191-4e2d-bfa9-008d4dc5725f</t>
         </is>
@@ -3010,77 +3036,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>90389b97-e11a-4ab4-99ba-a4d9312c24b2</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>84b80dad-747c-4973-b794-6e8a37c39f2a</t>
         </is>
@@ -3097,77 +3123,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>44915f0c-5875-41d7-a981-b0d094c8e3ad</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>e73db883-7dab-407c-abfc-2a59125c1c58</t>
         </is>
@@ -3184,77 +3210,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>d2a76427-58af-4f1f-b72d-7cd18a699dbe</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>0a5e0e0c-6062-48f6-af0e-1803cc3d9e42</t>
         </is>
@@ -3271,77 +3297,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>ff1982ad-1b8c-4758-8026-ab52e30c5a44</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>2d065764-e313-455f-8f71-2a11669ad3bd</t>
         </is>
@@ -3378,125 +3404,130 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="I39" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="K39" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K39" s="1" t="inlineStr">
+      <c r="L39" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="M39" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M39" s="1" t="inlineStr">
+      <c r="N39" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
+      <c r="O39" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="P39" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="Q39" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q39" s="1" t="inlineStr">
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R39" s="1" t="inlineStr">
+      <c r="S39" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S39" s="1" t="inlineStr">
+      <c r="T39" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T39" s="1" t="inlineStr">
+      <c r="U39" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
+      <c r="V39" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V39" s="1" t="inlineStr">
+      <c r="W39" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W39" s="1" t="inlineStr">
+      <c r="X39" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X39" s="1" t="inlineStr">
+      <c r="Y39" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
+      <c r="AA39" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB39" s="1" t="inlineStr">
+      <c r="AC39" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC39" s="1" t="inlineStr">
+      <c r="AD39" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3513,87 +3544,87 @@
           <t>1 ,1 ,1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>P.Jack Hammer</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>P.Jack Hammer</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>18,15,35</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>18,15,35</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>f6fd6876-0a23-4311-a47b-edcea5392c2d</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>d26f83e6-4030-4277-8587-1cd915b032b2</t>
         </is>
@@ -3610,92 +3641,92 @@
           <t>db+1 ,1 ,1 ,2</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-1 +1 +1 -20</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-1 +1 +1 -20</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+10 +12 +12 KD</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+10 +12 +12 KD</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+10 +12 +12 KD</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>+10 +12 +12 KD</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>18,25,25,40</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>18,25,25,40</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>lllm</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>lllm</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>8d45487a-dfa9-498f-90b6-3d5909ebfa7d</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>52f7f543-9e8d-49d7-8cfc-f4dffd3c4253</t>
         </is>
@@ -3712,97 +3743,97 @@
           <t>b,db,d,DF+1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Megaton Upper</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Megaton Upper</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>df26ebe1-ac11-478b-acd5-147c2956824b</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>b9ea6582-9cba-4c1a-bd63-351c4826c27c</t>
         </is>
@@ -3819,92 +3850,92 @@
           <t>hcf+1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Gigaton Punch</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Gigaton Punch</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>a030bc57-29e0-4774-8b99-ab4d2ffbc104</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>dd26c49f-1fac-490f-b121-a4e5271b37f9</t>
         </is>
@@ -3921,92 +3952,92 @@
           <t>DF+1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Uppercut Rush</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Uppercut Rush</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-11 -6 -8 -1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-11 -6 -8 -1</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>KD +5 +2 +9</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>KD +5 +2 +9</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>KD +5 +2 +9</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>KD +5 +2 +9</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>10,15,10,15</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>10,15,10,15</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>2ec0ed00-c481-4419-9c93-09500fb67872</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>97813b0e-9c95-4990-b631-4b77b824482d</t>
         </is>
@@ -4015,12 +4046,12 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,1</t>
+          <t>DF,1 ,2 ,1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4030,90 +4061,95 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>FC+DF+1,2,1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-6 -8 -2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-6 -8 -2</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>ea35c716-063e-4fe8-8dc3-4222f2c6ad18</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>5c3f1fbe-6f7b-4474-b49b-fe5fb34b6dbc</t>
         </is>
@@ -4130,87 +4166,87 @@
           <t>FC+df+1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Windmill</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Windmill</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-22 -22 -2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-22 -22 -2</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>12,15,15</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>12,15,15</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>e782cf5f-a503-4fb6-9041-13a98dd3fcf6</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>b54e5fae-ca15-405f-a538-e482d72081c3</t>
         </is>
@@ -4227,92 +4263,92 @@
           <t>FC+df+1 ,2 ,1 ,1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>– Windmill Backhand</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-22 -22 -2 +20</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>-12 -12 -12 KD</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>-12 -12 -12 KD</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>12,15,15,30</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>mmmh</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>CF GB</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>376237b4-a2cf-410e-9fce-72513f8ae579</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>bb4197bd-c25a-43ed-b442-1d8b575d6743</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>e782cf5f-a503-4fb6-9041-13a98dd3fcf6</t>
         </is>
@@ -4321,12 +4357,12 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Df+1 ,2</t>
+          <t>DF,1 ,2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4336,85 +4372,90 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>FC+DF+1,2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>Medium Hammer Rush</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Medium Hammer Rush</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-6 -8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-6 -8</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>a466b7af-98db-486e-8e9f-ca5cb4cec756</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>095fa58d-5a60-4556-89cb-a7dfe839fa96</t>
         </is>
@@ -4428,95 +4469,95 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,d+1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+          <t>DF,1 ,2 ,d+1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Medium Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-6 -8 -17</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+5 +2 -7</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+5 +2 -7</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>15,12,8</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>mmL</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>887fe401-14b1-4e28-9e57-bd2239a05793</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>829b69fd-97bb-4f8f-989a-8a465d1904b4</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>a466b7af-98db-486e-8e9f-ca5cb4cec756</t>
         </is>
@@ -4530,95 +4571,95 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,df+1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+          <t>DF,1 ,2 ,df+1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Medium Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-6 -8 -1</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+5 +2 +10</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>+5 +2 +10</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>5cc1af83-c369-4cec-b6b6-c5024d1ae4e1</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>1cbc86f2-a4e2-4572-a9e8-036559bde34d</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>a466b7af-98db-486e-8e9f-ca5cb4cec756</t>
         </is>
@@ -4632,90 +4673,90 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,f+1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+          <t>DF,1 ,2 ,f+1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Medium Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-6 -8 -17</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>+5 +2 -5</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>+5 +2 -5</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>15,12,12</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>168a9665-6d70-4891-8994-323277342b50</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>ea45819d-198d-4f9d-92fc-0bc783256bf0</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>a466b7af-98db-486e-8e9f-ca5cb4cec756</t>
         </is>
@@ -4732,87 +4773,87 @@
           <t>FC+1 ,1 ,1 ,2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>10,8,12,12</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>10,8,12,12</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>47822cd2-72ff-46ac-9fc7-ccbffa25845c</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>5d92c9ca-8b01-4857-beb1-7cc3b4c6fc2b</t>
         </is>
@@ -4829,92 +4870,92 @@
           <t>FC+1 ,1 ,1 ,2 ,d+1</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1 -7</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1 -7</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>10,8,12,12,8</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>LLmmL</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>c83119a2-6e51-4a65-8eed-68404fedfe4f</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>15b08d24-07bc-4ce4-a79d-d01403e81b58</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>47822cd2-72ff-46ac-9fc7-ccbffa25845c</t>
         </is>
@@ -4931,92 +4972,92 @@
           <t>FC+1 ,1 ,1 ,2 ,df+1</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1 +10</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1 +10</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>10,8,12,12,15</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>LLmmm</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>36ef000e-bc42-4acf-abc6-498af4941860</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>d1963515-9426-4e38-844b-701b61eb19cb</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>47822cd2-72ff-46ac-9fc7-ccbffa25845c</t>
         </is>
@@ -5033,87 +5074,87 @@
           <t>FC+1 ,1 ,1 ,2 ,f+1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1 -5</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>+2 +12 -2 +1 -5</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>10,8,12,12,12</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>LLmmh</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>461bcd3d-3e8a-43f6-ad57-2e71fb05e49a</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>b0ba5c6e-a849-4612-900e-233170274a74</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>47822cd2-72ff-46ac-9fc7-ccbffa25845c</t>
         </is>
@@ -5130,87 +5171,87 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Machine Elbow</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Machine Elbow</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>41c8e0cd-5fb1-4fb9-aba0-6496111325fa</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>fe95c1f3-6da8-4c21-a6bb-fd6687afed7d</t>
         </is>
@@ -5227,97 +5268,97 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Drill Upper</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Drill Upper</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>51d27e95-b4bc-49ba-94cc-95ce97570091</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>9e36172d-6fcc-4b81-a002-6aef7c524795</t>
         </is>
@@ -5334,87 +5375,87 @@
           <t>SS+1+2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Tornado Cutter</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Tornado Cutter</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-23 +2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-23 +2</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>-14 KD</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>-14 KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>-14 KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>-14 KD</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>87970594-f92d-4a9b-9094-b35c11accded</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>c6d3842c-463a-4e02-8c31-988f77ccf92d</t>
         </is>
@@ -5431,47 +5472,47 @@
           <t>db+1+2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Low Jab</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Low Jab</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>fe9b15d9-0797-4323-acf0-de71a4b2af82</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>9582af9e-5121-4ee5-b1a0-f6f114a3c385</t>
         </is>
@@ -5488,87 +5529,87 @@
           <t>1+2 &lt;1+2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-15 -22</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-15 -22</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>e0ed87d2-0438-440b-9444-91b4c432c09c</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>410bcd3d-e863-4ba7-b62b-12ba61c216e8</t>
         </is>
@@ -5585,87 +5626,87 @@
           <t>WS+1+2 &lt;1+2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-16 -15</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-16 -15</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>453807a1-22df-4342-96ea-a714db3619c4</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>30eead99-ae2c-4417-a3aa-3936e53f734c</t>
         </is>
@@ -5682,92 +5723,92 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Arm Scissors</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Arm Scissors</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>ac7e2ea3-fe48-4c93-a4c4-339727269bd1</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>04599616-1d26-4122-9380-7859b170c33d</t>
         </is>
@@ -5784,87 +5825,87 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Ground Drill</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Ground Drill</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-82 -70</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-82 -70</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-63 KD</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>-63 KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>-63 KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>-63 KD</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>11,22</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>11,22</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>220a4927-491e-4133-b752-76d61ed1b8f1</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>fe4383be-dbd1-4812-a8a3-75b63dc6dae9</t>
         </is>
@@ -5881,87 +5922,87 @@
           <t>d+1 ,2</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Tile Splitter - Deathfist</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Tile Splitter - Deathfist</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-7 -17</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-7 -17</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>-8 KD</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>-8 KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>+4 KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>+4 KD</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>15,25</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>15,25</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>23a46fe1-e0dd-4566-be50-efbaf21e9ecc</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>0f561cc6-2bb5-4061-b406-8636f71b9e74</t>
         </is>
@@ -5978,92 +6019,92 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Cemaho Chop</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Cemaho Chop</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>+13</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>+13</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>+13</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>+13</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>KS GB</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>8e944d3f-1e31-4ea7-889a-0be87731b01b</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>275aa17f-4306-494b-913f-490c7ed5c770</t>
         </is>
@@ -6072,12 +6113,12 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Df+2 ,1 ,2</t>
+          <t>DF,2 ,1 ,2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6087,85 +6128,90 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>FC+DF+2,1,2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>-9 -2 -9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-9 -2 -9</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>15,10,15</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>15,10,15</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>c9dfb893-8c3a-4500-8d7a-2fbeb592bd4a</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>4e65d43f-be3f-4ae3-99b9-9b2068aaf38e</t>
         </is>
@@ -6182,97 +6228,97 @@
           <t>2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>0 0 -15</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>0 0 -15</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>12,15,20</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>12,15,20</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>5958b4ac-a029-4674-b9a6-a62eb8a72d99</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>8c41cea3-7606-47eb-84f4-df3a09af76d9</t>
         </is>
@@ -6281,12 +6327,12 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6296,85 +6342,90 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>FC+df+2</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Short Hammer Rush</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Short Hammer Rush</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>dcee094c-31a9-4945-ad5c-863ebd27c9af</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>90915252-b8d2-4023-8e3e-443a6d5bb768</t>
         </is>
@@ -6388,95 +6439,95 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Df+2 ,d+1</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+          <t>DF,2 ,d+1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-13 -17</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>-2 -7</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>-2 -7</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>10,8</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>c0a11d95-ae6c-45f6-bc6f-22c3d5117b27</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>d8216f77-6249-4958-9c14-e1e0087817e2</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>dcee094c-31a9-4945-ad5c-863ebd27c9af</t>
         </is>
@@ -6490,95 +6541,95 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Df+2 ,df+1</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+          <t>DF,2 ,df+1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Short Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-13 -1</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>-2 +10</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>-2 +10</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>67adbbba-067b-4294-bcac-bbd3ca38a4cb</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>bee476ef-5b82-4ce5-9940-beb02b650995</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>dcee094c-31a9-4945-ad5c-863ebd27c9af</t>
         </is>
@@ -6592,90 +6643,90 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Df+2 ,f+1</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+          <t>DF,2 ,f+1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Short Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-13 -17</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>-2 -5</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>-2 -5</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>10,12</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>3e1f024f-c9d3-4ecf-913e-d44dc0a0d843</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>c52d2e31-9cce-4bb4-91aa-894cc1ab150a</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>dcee094c-31a9-4945-ad5c-863ebd27c9af</t>
         </is>
@@ -6692,92 +6743,92 @@
           <t>DF+2 ,1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Hammer Uppercut Rush</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Hammer Uppercut Rush</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-11 -13 -1 -6</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-11 -13 -1 -6</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>0 -2 +9 +2</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>0 -2 +9 +2</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>0 -2 +9 +2</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>0 -2 +9 +2</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>10,15,12,15</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>10,15,12,15</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>ed86be92-d9ae-4805-bba8-9d95535d4379</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>73827643-700f-4300-99bc-86e87fec30c0</t>
         </is>
@@ -6794,92 +6845,92 @@
           <t>b,db,d,DF+2</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Megaton Punch</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Megaton Punch</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>d31a40fd-3ca6-4512-ae23-679a3c8ea00d</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>4d243f66-9d5a-4074-bc67-91414be42a2d</t>
         </is>
@@ -6896,92 +6947,92 @@
           <t>SS+2</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Drill Punch</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Drill Punch</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>Throw on a clean hit.</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>55a6e884-06b8-44bd-8749-e7ebc4291282</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>8293294b-d52e-4125-986d-d756461f85af</t>
         </is>
@@ -6998,92 +7049,92 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Hip Press</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Hip Press</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>If the Hip Press Misses the opponent, Prototype can chain into Sit Down extentions.</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>2af57a90-0d6d-453d-8855-32e5ed5c107d</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>7f331f78-b7b1-4f34-8ee7-2bf862cd7de1</t>
         </is>
@@ -7100,47 +7151,47 @@
           <t>d+3+4</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>26ea1627-a6f6-4d5d-b6d6-de091319d6c7</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>bc6d4022-042d-4e84-96e1-769d02b97185</t>
         </is>
@@ -7157,52 +7208,52 @@
           <t>d+3+4,B</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Sit Down – Roll Back</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>5bfee60d-802b-4779-9da2-9cb6ec27ebd1</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>3242ab71-7917-46d2-b9d2-d2fd8fbb7081</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>26ea1627-a6f6-4d5d-b6d6-de091319d6c7</t>
         </is>
@@ -7219,52 +7270,52 @@
           <t>d+3+4,F</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Sit Down – Roll Forward</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>13a41232-90ab-4c86-9cc8-e7c06c5481d1</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>101709ae-f6ed-4614-b839-1ceb8ae89971</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>26ea1627-a6f6-4d5d-b6d6-de091319d6c7</t>
         </is>
@@ -7281,190 +7332,210 @@
           <t>d+3+4 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>d+3+4,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Sit Down – Sitting Punches</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>-,10,10,10,10</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>-llll</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>e9e851c4-f29f-45e8-a1a6-2c142665c2c9</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>49aa4e61-5e06-452b-b88a-67d97aa29d2e</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>26ea1627-a6f6-4d5d-b6d6-de091319d6c7</t>
         </is>
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+          <t>d+1+2</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>829f648f-350b-4760-8879-7871be91e9f6</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>44936cff-8989-4dd5-ad50-d29ef0b197e4</t>
         </is>
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
@@ -7472,95 +7543,105 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KND d+1+2 ,1 ,2 ,1 ,2</t>
+          <t>d+1+2 ,1 ,2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>KND d+1+2,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down – Sitting Punches</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>+7 -45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>+11 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>+11 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>12,10,10,10,10</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>mllll</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>11bbf526-cf26-4edd-a2bf-323285601c6c</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>f6b6823f-f0c6-428b-a85e-e60f7e585dd8</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>829f648f-350b-4760-8879-7871be91e9f6</t>
         </is>
@@ -7577,97 +7658,97 @@
           <t>f+3+4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Digital Hans Headslide</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Digital Hans Headslide</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>-110</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-110</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>(m_L)</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>(m_L)</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>Hits mid at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>4c31f073-e52b-4c4a-9117-e335864330d1</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>9e61b39e-f538-4df1-a822-052c94c208aa</t>
         </is>
@@ -7684,52 +7765,52 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Clock Up</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Clock Up</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Repels all attacks.</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>3b432f29-30fd-4111-becb-d3a6c5a325b3</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>a27549c5-9f3d-4730-9b54-25cee3f62452</t>
         </is>
@@ -7746,52 +7827,52 @@
           <t>b+1+2~f</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>– Cancel</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Clock Up – Cancel</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>75ac5c08-494a-4b11-a671-93f62f3d8acd</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>deae7d8e-d95e-42b3-8c96-506cd1abf1da</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
+      <c r="AC84" t="inlineStr">
         <is>
           <t>3b432f29-30fd-4111-becb-d3a6c5a325b3</t>
         </is>
@@ -7828,125 +7909,130 @@
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
+      <c r="H87" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H87" s="1" t="inlineStr">
+      <c r="I87" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I87" s="1" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J87" s="1" t="inlineStr">
+      <c r="K87" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K87" s="1" t="inlineStr">
+      <c r="L87" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L87" s="1" t="inlineStr">
+      <c r="M87" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M87" s="1" t="inlineStr">
+      <c r="N87" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N87" s="1" t="inlineStr">
+      <c r="O87" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O87" s="1" t="inlineStr">
+      <c r="P87" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P87" s="1" t="inlineStr">
+      <c r="Q87" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q87" s="1" t="inlineStr">
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R87" s="1" t="inlineStr">
+      <c r="S87" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S87" s="1" t="inlineStr">
+      <c r="T87" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T87" s="1" t="inlineStr">
+      <c r="U87" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U87" s="1" t="inlineStr">
+      <c r="V87" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V87" s="1" t="inlineStr">
+      <c r="W87" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W87" s="1" t="inlineStr">
+      <c r="X87" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X87" s="1" t="inlineStr">
+      <c r="Y87" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y87" s="1" t="inlineStr">
+      <c r="Z87" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z87" s="1" t="inlineStr">
+      <c r="AA87" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA87" s="1" t="inlineStr">
+      <c r="AB87" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB87" s="1" t="inlineStr">
+      <c r="AC87" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC87" s="1" t="inlineStr">
+      <c r="AD87" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7963,82 +8049,82 @@
           <t>f+4 ~1</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Dark Greeting</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Dark Greeting</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>0b25bc01-f4f8-4c02-8e24-fb76a48c41b3</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>634bbcea-52ea-4056-888f-ec53cfec7cad</t>
         </is>
@@ -8055,77 +8141,77 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Gigaton Stomp</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Gigaton Stomp</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>8d27a14b-8380-4f1c-8ff0-ee1395982bca</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>8c05fa65-817a-48ae-9925-aac6fd57163b</t>
         </is>
@@ -8142,77 +8228,77 @@
           <t>3+4&gt;3+4</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Double Thrust Gigaton Stomp</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Double Thrust Gigaton Stomp</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>1dce0a83-a7bf-4962-ac9a-d8cd9de5f6ae</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>cbdc31a5-0f5d-4f16-9cad-b8c245bcc20e</t>
         </is>
@@ -8229,77 +8315,77 @@
           <t>3+4&gt;3+4 ,3+4</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Triple Thrust Gigaton Stomp</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Triple Thrust Gigaton Stomp</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>36e7491c-7cd1-43d8-a32f-27a87ade3345</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>97f3a33b-52c4-46fb-83fe-f84d3ec54e5c</t>
         </is>
@@ -8316,67 +8402,67 @@
           <t>hcf</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Gigaton Start Up</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Gigaton Start Up</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>3a1930ac-a3a1-4c51-bd78-c338f3e86f0e</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>8213b614-e62d-4eba-9f97-d89db2e9f00c</t>
         </is>
@@ -8393,77 +8479,77 @@
           <t>hcf,b,db,d,df,f,uf,u,ub</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>– Wind Up</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>Can be repeated up to 5 times.</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>1a53eefa-8ff3-42ca-af94-fda8eb3b62ca</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>8c8bbec7-5077-4daf-adc6-79937fa5d1bd</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
+      <c r="AC93" t="inlineStr">
         <is>
           <t>3a1930ac-a3a1-4c51-bd78-c338f3e86f0e</t>
         </is>
@@ -8480,77 +8566,77 @@
           <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>–– Gigaton Punch</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>-,-,40</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>--!</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>1be3e5f2-abc0-4708-ac1e-330affc967c3</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>60f4bdf1-ab3d-4f9d-9a10-45adc55f09e0</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
+      <c r="AC94" t="inlineStr">
         <is>
           <t>1a53eefa-8ff3-42ca-af94-fda8eb3b62ca</t>
         </is>
@@ -8567,52 +8653,52 @@
           <t>5~u</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Giga Tag Stomp</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Giga Tag Stomp</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>When tagging in Prototype Jack.</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>7967f622-5e62-4815-ad6d-25d144ee02dd</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>97ede0be-8269-403a-9c80-54e37bec46c4</t>
         </is>
@@ -8649,125 +8735,130 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="H98" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H98" s="1" t="inlineStr">
+      <c r="I98" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I98" s="1" t="inlineStr">
+      <c r="J98" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J98" s="1" t="inlineStr">
+      <c r="K98" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="M98" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
+      <c r="P98" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q98" s="1" t="inlineStr">
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
+      <c r="S98" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S98" s="1" t="inlineStr">
+      <c r="T98" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T98" s="1" t="inlineStr">
+      <c r="U98" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U98" s="1" t="inlineStr">
+      <c r="V98" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V98" s="1" t="inlineStr">
+      <c r="W98" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W98" s="1" t="inlineStr">
+      <c r="X98" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X98" s="1" t="inlineStr">
+      <c r="Y98" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y98" s="1" t="inlineStr">
+      <c r="Z98" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z98" s="1" t="inlineStr">
+      <c r="AA98" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA98" s="1" t="inlineStr">
+      <c r="AB98" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB98" s="1" t="inlineStr">
+      <c r="AC98" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC98" s="1" t="inlineStr">
+      <c r="AD98" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8784,42 +8875,42 @@
           <t>d+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,1+2 ,1+2</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>4e36f2e9-e904-45da-b205-e22a2d153bbd</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>4e36f2e9-e904-45da-b205-e22a2d153bbd</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
+      <c r="AD99" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
